--- a/frontend/public/PackingList_sample.xlsx
+++ b/frontend/public/PackingList_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\valueonsys\workspace\vos-oog\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8084E5D4-0753-42B0-B32E-D46A3B1D3003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0578745-1121-4B61-A578-26EC0614625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19600" yWindow="-18710" windowWidth="20660" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14540" yWindow="-21600" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PL" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
-  <si>
-    <t>Length
-가로</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Width
-세로</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>Height
 높이</t>
@@ -71,25 +61,74 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>R/D Tank Body (Head-1)</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>System Pump (Head-1)</t>
-  </si>
-  <si>
     <t>HEAD</t>
+  </si>
+  <si>
+    <t>Box Dimension(㎜)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item Type
+일반/진공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Weight
+중량(㎏)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gross Weight
+중량(㎏)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remarks
+비고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length
+길이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Width
+폭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>System Pump B1 (2대)</t>
+  </si>
+  <si>
+    <t>진공</t>
+  </si>
+  <si>
+    <t>HEADER B1/C1</t>
+  </si>
+  <si>
+    <t>일반</t>
+  </si>
+  <si>
+    <t>B헤더베이스,1차흡입배관,버블링배관</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0_);\(0\)"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -218,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -232,11 +271,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,131 +587,229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.69921875" customWidth="1"/>
     <col min="2" max="2" width="30.69921875" customWidth="1"/>
-    <col min="3" max="8" width="10.69921875" customWidth="1"/>
-    <col min="9" max="9" width="20.69921875" customWidth="1"/>
+    <col min="3" max="13" width="10.69921875" customWidth="1"/>
+    <col min="14" max="14" width="20.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="M2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>6500</v>
+      </c>
+      <c r="D3">
+        <v>1500</v>
+      </c>
+      <c r="E3">
+        <v>1500</v>
+      </c>
+      <c r="F3">
+        <v>2440</v>
+      </c>
+      <c r="G3">
+        <v>1860</v>
+      </c>
+      <c r="H3">
+        <v>1150</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>5.2191599999999996</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>1000</v>
+      </c>
+      <c r="M3">
+        <v>1208.7664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>6500</v>
+      </c>
+      <c r="D4">
+        <v>1500</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
+        <v>8000</v>
+      </c>
+      <c r="G4">
+        <v>2250</v>
+      </c>
+      <c r="H4">
+        <v>2520</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>45.36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4">
+        <v>4000</v>
+      </c>
+      <c r="M4">
+        <v>5814.4</v>
+      </c>
+      <c r="N4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>3000</v>
+      </c>
+      <c r="D5">
+        <v>3000</v>
+      </c>
+      <c r="E5">
+        <v>2000</v>
+      </c>
+      <c r="F5">
+        <v>3660</v>
+      </c>
+      <c r="G5">
+        <v>2260</v>
+      </c>
+      <c r="H5">
+        <v>2400</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>9000</v>
-      </c>
-      <c r="D3">
+      <c r="J5">
+        <v>19.851839999999999</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5">
         <v>3000</v>
       </c>
-      <c r="E3">
-        <v>3000</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>11178.720000000001</v>
-      </c>
-      <c r="H3">
-        <v>104.468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>5700</v>
-      </c>
-      <c r="D4">
-        <v>2300</v>
-      </c>
-      <c r="E4">
-        <v>3300</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>12196</v>
-      </c>
-      <c r="H4">
-        <v>54.9</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
+      <c r="M5">
+        <v>3794.0735999999997</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
